--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Documentación/TEC_SIGET.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Documentación/TEC_SIGET.xlsx
@@ -429,12 +429,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="0 &quot;HH&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot; HH&quot;"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot; HH/semana&quot;"/>
+    <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="170">
     <font>
       <sz val="11.000000"/>
       <name val="Carlito"/>
@@ -478,8 +482,767 @@
       <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,6 +1284,198 @@
         <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -535,7 +1490,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="196">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -616,6 +1571,510 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="14" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="15" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="16" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="17" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="18" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="22" fillId="6" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="23" fillId="6" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="24" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="11" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="12" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="28" fillId="13" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="29" fillId="14" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="30" fillId="15" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="31" fillId="16" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="32" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="35" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="36" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="37" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="38" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="39" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="40" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="41" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="42" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="43" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="44" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="45" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="46" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="47" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="48" fillId="17" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="49" fillId="18" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="19" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="51" fillId="20" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="52" fillId="21" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="53" fillId="22" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="54" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="55" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="56" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="57" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="58" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="59" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="60" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="61" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="62" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="63" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="64" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="65" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="66" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="67" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="68" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="69" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="70" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="71" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="72" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="73" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="74" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="75" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="76" fillId="6" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="77" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="78" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="79" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="80" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="81" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="82" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="83" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="84" fillId="23" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="85" fillId="24" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="86" fillId="25" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="87" fillId="26" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="88" fillId="27" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="89" fillId="28" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="90" fillId="29" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="91" fillId="30" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="92" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="93" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="67" fillId="0" borderId="0" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="94" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="95" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="96" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="97" fillId="6" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="98" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="99" fillId="31" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="100" fillId="32" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="101" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="102" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="103" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="104" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="105" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="106" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="107" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="108" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="109" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="110" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="111" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="112" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="113" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="114" fillId="34" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="115" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="116" fillId="36" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="117" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="118" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="119" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="120" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="121" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="122" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="123" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="124" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="125" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="126" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="127" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="128" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="129" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="130" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="131" fillId="6" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="132" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="133" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="134" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="135" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="136" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="137" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="138" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="139" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="140" fillId="6" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="141" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="142" fillId="37" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="143" fillId="38" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="144" fillId="39" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="right"/>
+    </xf>
+    <xf fontId="145" fillId="40" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="146" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="147" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="148" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="149" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="150" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="151" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="152" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="153" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="154" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="155" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="156" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="157" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="158" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="159" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="160" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="161" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="162" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="163" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="164" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="165" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="166" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="167" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="168" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="169" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="147" fillId="0" borderId="0" numFmtId="170" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="151" fillId="0" borderId="0" numFmtId="170" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="155" fillId="0" borderId="0" numFmtId="168" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="159" fillId="0" borderId="0" numFmtId="168" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1160,12 +2619,13 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" ht="28.5">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
+      <c r="B4" s="2" t="str">
+        <f>'Supuestos'!B4</f>
+        <v>7 sprints / 13/08/2026 al 05/11/2026</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="5" t="s">
@@ -1203,6 +2663,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="7">
+        <f>'HH por Integrante'!C7</f>
         <v>900</v>
       </c>
       <c r="C6" s="2"/>
@@ -1292,8 +2753,10 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>La estimación de referencia es de 900 HH, distribuidas entre tres integrantes y siete sprints. El costo del trabajo se valoriza con una tarifa referencial. El seguimiento acumula las horas registradas y proyecta el costo pendiente. El presupuesto base y la reserva de contingencia se mantienen separados.</t>
+        </is>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1334,12 +2797,16 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>Seguimiento de ejecución</t>
+        </is>
+      </c>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="73"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
@@ -1353,53 +2820,109 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="104" t="inlineStr">
+        <is>
+          <t>HH registradas</t>
+        </is>
+      </c>
+      <c r="B18" s="112">
+        <f>'Seguimiento por Sprint'!D11</f>
+        <v>534.5</v>
+      </c>
+      <c r="C18" s="76"/>
+      <c r="D18" s="107" t="inlineStr">
+        <is>
+          <t>Costo HH registrado</t>
+        </is>
+      </c>
+      <c r="E18" s="115">
+        <f>'Costos y Presupuesto'!C19</f>
+        <v>8017500</v>
+      </c>
+      <c r="F18" s="79"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t>HH pendientes (plan)</t>
+        </is>
+      </c>
+      <c r="B19" s="113">
+        <f>SUMIF('Seguimiento por Sprint'!D4:D10,"",'Seguimiento por Sprint'!C4:C10)</f>
+        <v>300</v>
+      </c>
+      <c r="C19" s="82"/>
+      <c r="D19" s="108" t="inlineStr">
+        <is>
+          <t>Desarrollo pendiente (plan)</t>
+        </is>
+      </c>
+      <c r="E19" s="116">
+        <f>'Costos y Presupuesto'!C20</f>
+        <v>4500000</v>
+      </c>
+      <c r="F19" s="85"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="106" t="inlineStr">
+        <is>
+          <t>Sprints con horas registradas</t>
+        </is>
+      </c>
+      <c r="B20" s="114">
+        <f>COUNT('Seguimiento por Sprint'!D4:D10)</f>
+        <v>6</v>
+      </c>
+      <c r="C20" s="88"/>
+      <c r="D20" s="109" t="inlineStr">
+        <is>
+          <t>Otros costos estimados</t>
+        </is>
+      </c>
+      <c r="E20" s="117">
+        <f>'Costos y Presupuesto'!C21</f>
+        <v>1200000</v>
+      </c>
+      <c r="F20" s="91"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="92"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="120" t="inlineStr">
+        <is>
+          <t>Costo total proyectado</t>
+        </is>
+      </c>
+      <c r="E21" s="121">
+        <f>'Costos y Presupuesto'!C22</f>
+        <v>13717500</v>
+      </c>
+      <c r="F21" s="97"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="98"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="111" t="inlineStr">
+        <is>
+          <t>Holgura del presupuesto</t>
+        </is>
+      </c>
+      <c r="E22" s="119">
+        <f>'Costos y Presupuesto'!C23</f>
+        <v>2282500</v>
+      </c>
+      <c r="F22" s="103"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
@@ -1414,22 +2937,26 @@
       <c r="H23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="A24" s="122" t="inlineStr">
+        <is>
+          <t>El costo registrado valoriza el esfuerzo. La proyección incorpora el trabajo pendiente y los costos no laborales estimados.</t>
+        </is>
+      </c>
+      <c r="B24" s="123"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="127"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="A25" s="128"/>
+      <c r="B25" s="129"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="133"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
@@ -1484,10 +3011,12 @@
       <c r="H30" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A12:F14"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A24:F25"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1559,6 +3088,7 @@
         <v>300</v>
       </c>
       <c r="D4" s="6">
+        <f>'Resumen TEC'!$B$7</f>
         <v>15000</v>
       </c>
       <c r="E4" s="6">
@@ -1580,6 +3110,7 @@
         <v>300</v>
       </c>
       <c r="D5" s="6">
+        <f>'Resumen TEC'!$B$7</f>
         <v>15000</v>
       </c>
       <c r="E5" s="6">
@@ -1601,6 +3132,7 @@
         <v>300</v>
       </c>
       <c r="D6" s="6">
+        <f>'Resumen TEC'!$B$7</f>
         <v>15000</v>
       </c>
       <c r="E6" s="6">
@@ -2385,8 +3917,10 @@
       <c r="A4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>54</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>HH planificadas × tarifa referencial</t>
+        </is>
       </c>
       <c r="C4" s="6">
         <f>'HH por Integrante'!E7</f>
@@ -2532,7 +4066,7 @@
         <v>71</v>
       </c>
       <c r="C12" s="21">
-        <f>C11*10%</f>
+        <f>C11*'Resumen TEC'!$E$7</f>
         <v>1600000</v>
       </c>
       <c r="D12" s="20" t="s">
@@ -2595,10 +4129,14 @@
       <c r="H16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="134" t="inlineStr">
+        <is>
+          <t>Seguimiento y proyección de costos</t>
+        </is>
+      </c>
+      <c r="B17" s="135"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="137"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -2614,51 +4152,118 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="138" t="inlineStr">
+        <is>
+          <t>Desarrollo registrado</t>
+        </is>
+      </c>
+      <c r="B19" s="139" t="inlineStr">
+        <is>
+          <t>HH registradas × tarifa</t>
+        </is>
+      </c>
+      <c r="C19" s="158">
+        <f>'Seguimiento por Sprint'!G11</f>
+        <v>8017500</v>
+      </c>
+      <c r="D19" s="141" t="inlineStr">
+        <is>
+          <t>Valorización acumulada de los sprints con horas registradas.</t>
+        </is>
+      </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="142" t="inlineStr">
+        <is>
+          <t>Desarrollo pendiente (plan)</t>
+        </is>
+      </c>
+      <c r="B20" s="143" t="inlineStr">
+        <is>
+          <t>HH sin registro × tarifa</t>
+        </is>
+      </c>
+      <c r="C20" s="159">
+        <f>'Resumen TEC'!B19*'Resumen TEC'!$B$7</f>
+        <v>4500000</v>
+      </c>
+      <c r="D20" s="145" t="inlineStr">
+        <is>
+          <t>Esfuerzo planificado de los sprints pendientes de cierre.</t>
+        </is>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="146" t="inlineStr">
+        <is>
+          <t>Otros costos estimados</t>
+        </is>
+      </c>
+      <c r="B21" s="147" t="inlineStr">
+        <is>
+          <t>Infraestructura, servicios y equipos</t>
+        </is>
+      </c>
+      <c r="C21" s="160">
+        <f>SUM(C5:C8)</f>
+        <v>1200000</v>
+      </c>
+      <c r="D21" s="149" t="inlineStr">
+        <is>
+          <t>Estimaciones no laborales del presupuesto.</t>
+        </is>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="163" t="inlineStr">
+        <is>
+          <t>COSTO TOTAL PROYECTADO</t>
+        </is>
+      </c>
+      <c r="B22" s="164"/>
+      <c r="C22" s="165">
+        <f>SUM(C19:C21)</f>
+        <v>13717500</v>
+      </c>
+      <c r="D22" s="166" t="inlineStr">
+        <is>
+          <t>Desarrollo registrado, trabajo pendiente y otros costos estimados.</t>
+        </is>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="154" t="inlineStr">
+        <is>
+          <t>Holgura del presupuesto base</t>
+        </is>
+      </c>
+      <c r="B23" s="155"/>
+      <c r="C23" s="162">
+        <f>C11-C22</f>
+        <v>2282500</v>
+      </c>
+      <c r="D23" s="157" t="inlineStr">
+        <is>
+          <t>Presupuesto base menos costo total proyectado.</t>
+        </is>
+      </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -2735,9 +4340,10 @@
       <c r="H30" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2760,8 +4366,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>77</v>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Seguimiento de tiempo, esfuerzo y costo por sprint</t>
+        </is>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2781,7 +4389,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>78</v>
       </c>
@@ -2791,8 +4399,10 @@
       <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>80</v>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>HH registradas</t>
+        </is>
       </c>
       <c r="E3" s="12" t="s">
         <v>81</v>
@@ -2800,312 +4410,312 @@
       <c r="F3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>83</v>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Costo HH registrado</t>
+        </is>
       </c>
       <c r="H3" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="54" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>86</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>13/08–26/08: Definición y fundamentación del proyecto.</t>
+        </is>
       </c>
       <c r="C4" s="7">
         <v>100</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="28">
         <v>32</v>
       </c>
-      <c r="E4" s="7">
-        <f t="shared" ref="E4:E9" si="5">IF(D4="","",D4-C4)</f>
+      <c r="E4" s="29">
+        <f>IF(ISNUMBER(D4),D4-C4,"")</f>
         <v>-68</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" ref="F4:F9" si="6">C4*15000</f>
+        <f>C4*'Resumen TEC'!$B$7</f>
         <v>1500000</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" ref="G4:G9" si="7">IF(D4="","",D4*15000)</f>
+        <f>IF(ISNUMBER(D4),D4*'Resumen TEC'!$B$7,"")</f>
         <v>480000</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>89</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>27/08–09/09: Requerimientos, backlog, arquitectura y diseño.</t>
+        </is>
       </c>
       <c r="C5" s="7">
         <v>100</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="30">
         <v>90</v>
       </c>
-      <c r="E5" s="7">
-        <f t="shared" si="5"/>
+      <c r="E5" s="31">
+        <f>IF(ISNUMBER(D5),D5-C5,"")</f>
         <v>-10</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="6"/>
+        <f>C5*'Resumen TEC'!$B$7</f>
         <v>1500000</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="7"/>
+        <f>IF(ISNUMBER(D5),D5*'Resumen TEC'!$B$7,"")</f>
         <v>1350000</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>91</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>10/09–14/09: Repositorio, Docker, PostgreSQL y arquitectura inicial.</t>
+        </is>
       </c>
       <c r="C6" s="7">
         <v>100</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="32">
         <v>56</v>
       </c>
-      <c r="E6" s="7">
-        <f t="shared" si="5"/>
+      <c r="E6" s="33">
+        <f>IF(ISNUMBER(D6),D6-C6,"")</f>
         <v>-44</v>
       </c>
       <c r="F6" s="6">
-        <f t="shared" si="6"/>
+        <f>C6*'Resumen TEC'!$B$7</f>
         <v>1500000</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="7"/>
+        <f>IF(ISNUMBER(D6),D6*'Resumen TEC'!$B$7,"")</f>
         <v>840000</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>93</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>15/09–28/09: Autenticación, acceso e integración del entorno.</t>
+        </is>
       </c>
       <c r="C7" s="7">
         <v>100</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="34">
         <v>51</v>
       </c>
-      <c r="E7" s="7">
-        <f t="shared" si="5"/>
+      <c r="E7" s="35">
+        <f>IF(ISNUMBER(D7),D7-C7,"")</f>
         <v>-49</v>
       </c>
       <c r="F7" s="6">
-        <f t="shared" si="6"/>
+        <f>C7*'Resumen TEC'!$B$7</f>
         <v>1500000</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="7"/>
+        <f>IF(ISNUMBER(D7),D7*'Resumen TEC'!$B$7,"")</f>
         <v>765000</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>96</v>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>29/09–18/10: Activos, asignaciones, entregas, devoluciones y tickets iniciales.</t>
+        </is>
       </c>
       <c r="C8" s="7">
         <v>100</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+      <c r="D8" s="36">
+        <v>230</v>
+      </c>
+      <c r="E8" s="37">
+        <f>IF(ISNUMBER(D8),D8-C8,"")</f>
+        <v>130</v>
       </c>
       <c r="F8" s="6">
-        <f t="shared" si="6"/>
+        <f>C8*'Resumen TEC'!$B$7</f>
         <v>1500000</v>
       </c>
-      <c r="G8" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="G8" s="6">
+        <f>IF(ISNUMBER(D8),D8*'Resumen TEC'!$B$7,"")</f>
+        <v>3450000</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>100</v>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>19/10–26/10: Escritorio, tickets y OT, auditoría, correo, avisos, CSAT y catálogos.</t>
+        </is>
       </c>
       <c r="C9" s="7">
         <v>100</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+      <c r="D9" s="38">
+        <v>75.5</v>
+      </c>
+      <c r="E9" s="39">
+        <f>IF(ISNUMBER(D9),D9-C9,"")</f>
+        <v>-24.5</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="6"/>
+        <f>C9*'Resumen TEC'!$B$7</f>
         <v>1500000</v>
       </c>
-      <c r="G9" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="G9" s="6">
+        <f>IF(ISNUMBER(D9),D9*'Resumen TEC'!$B$7,"")</f>
+        <v>1132500</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>103</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>27/10–05/11: Reparación, repuestos, QR, reportes, seguridad, QA y cierre.</t>
+        </is>
       </c>
       <c r="C10" s="7">
-        <v>100</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="str">
-        <f t="shared" ref="E10:E13" si="8">IF(D10="","",D10-C10)</f>
+        <v>300</v>
+      </c>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41" t="str">
+        <f>IF(ISNUMBER(D10),D10-C10,"")</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f t="shared" ref="F10:F12" si="9">C10*15000</f>
-        <v>1500000</v>
+        <f>C10*'Resumen TEC'!$B$7</f>
+        <v>4500000</v>
       </c>
       <c r="G10" s="6" t="str">
-        <f t="shared" ref="G10:G12" si="10">IF(D10="","",D10*15000)</f>
+        <f>IF(ISNUMBER(D10),D10*'Resumen TEC'!$B$7,"")</f>
         <v/>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="7">
-        <v>100</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f t="shared" si="9"/>
-        <v>1500000</v>
-      </c>
-      <c r="G11" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>101</v>
-      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" s="46">
+        <f>SUM(C4:C10)</f>
+        <v>900</v>
+      </c>
+      <c r="D11" s="47">
+        <f>IF(COUNT(D4:D10)=0,"",SUM(D4:D10))</f>
+        <v>534.5</v>
+      </c>
+      <c r="E11" s="48">
+        <f>IF(COUNT(D4:D10)=0,"",SUM(E4:E10))</f>
+        <v>-65.5</v>
+      </c>
+      <c r="F11" s="49">
+        <f>SUM(F4:F10)</f>
+        <v>13500000</v>
+      </c>
+      <c r="G11" s="50">
+        <f>IF(COUNT(G4:G10)=0,"",SUM(G4:G10))</f>
+        <v>8017500</v>
+      </c>
+      <c r="H11" s="51"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="7">
-        <v>100</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f t="shared" si="9"/>
-        <v>1500000</v>
-      </c>
-      <c r="G12" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>101</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="13">
-        <f>SUM(C4:C12)</f>
-        <v>900</v>
-      </c>
-      <c r="D13" s="13">
-        <f>IF(COUNT(D4:D12)=0,"",SUM(D4:D12))</f>
-        <v>229</v>
-      </c>
-      <c r="E13" s="13">
-        <f t="shared" si="8"/>
-        <v>-671</v>
-      </c>
-      <c r="F13" s="10">
-        <f>SUM(F4:F12)</f>
-        <v>13500000</v>
-      </c>
-      <c r="G13" s="10">
-        <f>IF(COUNT(G4:G12)=0,"",SUM(G4:G12))</f>
-        <v>3435000</v>
-      </c>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="52" t="inlineStr">
+        <is>
+          <t>Las HH registradas corresponden a los registros de actividades de cada sprint y son estimaciones de dedicación. Se incorporan al seguimiento al cerrar el sprint.</t>
+        </is>
+      </c>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>La desviación acumulada compara únicamente los sprints con horas registradas. El Sprint 7 concentra las actividades pendientes de desarrollo, integración, pruebas y cierre.</t>
+        </is>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
     </row>
     <row r="16">
       <c r="A16" s="2"/>
@@ -3258,8 +4868,10 @@
       <c r="H30" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -3272,7 +4884,7 @@
           <x14:formula1>
             <xm:f>"No iniciado,En curso,Completado,Bloqueado"</xm:f>
           </x14:formula1>
-          <xm:sqref>H4:H12</xm:sqref>
+          <xm:sqref>H4:H10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3330,18 +4942,23 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Periodo del proyecto</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>B18&amp;" sprints / "&amp;TEXT(B15,"dd/mm/yyyy")&amp;" al "&amp;TEXT(B16,"dd/mm/yyyy")</f>
+        <v>7 sprints / 13/08/2026 al 05/11/2026</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>114</v>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Planificación vigente de siete sprints.</t>
+        </is>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3385,17 +5002,22 @@
       <c r="H6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>121</v>
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Dedicación media planificada</t>
+        </is>
+      </c>
+      <c r="B7" s="167">
+        <f>'HH por Integrante'!C4/B17</f>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>123</v>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>HH por integrante / semanas del periodo.</t>
+        </is>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -3500,61 +5122,122 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="168" t="inlineStr">
+        <is>
+          <t>Inicio del periodo</t>
+        </is>
+      </c>
+      <c r="B15" s="192">
+        <v>46247.0</v>
+      </c>
+      <c r="C15" s="170" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D15" s="171"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="172" t="inlineStr">
+        <is>
+          <t>Cierre del periodo</t>
+        </is>
+      </c>
+      <c r="B16" s="193">
+        <v>46331.0</v>
+      </c>
+      <c r="C16" s="174" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D16" s="175"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="176" t="inlineStr">
+        <is>
+          <t>Duración en semanas</t>
+        </is>
+      </c>
+      <c r="B17" s="194">
+        <f>(B16-B15)/7</f>
+        <v>12</v>
+      </c>
+      <c r="C17" s="178" t="inlineStr">
+        <is>
+          <t>Derivado</t>
+        </is>
+      </c>
+      <c r="D17" s="179"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="180" t="inlineStr">
+        <is>
+          <t>Número de sprints</t>
+        </is>
+      </c>
+      <c r="B18" s="195">
+        <v>7</v>
+      </c>
+      <c r="C18" s="182" t="inlineStr">
+        <is>
+          <t>Planificado</t>
+        </is>
+      </c>
+      <c r="D18" s="183" t="inlineStr">
+        <is>
+          <t>Las actividades pendientes se concentran en el Sprint 7.</t>
+        </is>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="184"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="187"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="188" t="inlineStr">
+        <is>
+          <t>Criterio de seguimiento</t>
+        </is>
+      </c>
+      <c r="B20" s="189" t="inlineStr">
+        <is>
+          <t>HH estimadas de dedicación según los registros de actividades de cada sprint.</t>
+        </is>
+      </c>
+      <c r="C20" s="190" t="inlineStr">
+        <is>
+          <t>Registro</t>
+        </is>
+      </c>
+      <c r="D20" s="191" t="inlineStr">
+        <is>
+          <t>El costo de HH es una valorización referencial del esfuerzo.</t>
+        </is>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
